--- a/static/standards-correlations/Indiana_CS1_State_Standards.xlsx
+++ b/static/standards-correlations/Indiana_CS1_State_Standards.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Crosswalk" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Legend &amp; Attribution" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Crosswalk" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Legend &amp; Attribution" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Crosswalk'!$A$4:$I$35</definedName>
@@ -565,10 +565,11 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Scored against full lab bodies | C and Python tracks | Discovery Projects | Indiana foundational HS computer science course</t>
-        </is>
-      </c>
-    </row>
+          <t>Scored against full lab bodies | C and Python tracks | Introductory Projects | Indiana foundational HS computer science course</t>
+        </is>
+      </c>
+    </row>
+    <row r="3"/>
     <row r="4" ht="32" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -602,7 +603,7 @@
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>Discovery Projects</t>
+          <t>Introductory Projects</t>
         </is>
       </c>
       <c r="H4" s="3" t="inlineStr">
@@ -702,7 +703,7 @@
       </c>
       <c r="I6" s="8" t="inlineStr">
         <is>
-          <t>Discovery Systems 12 covers how computing changed the world and Ext 5.2D (Should It Exist?) examines a current technology in context. A historical survey is not taught.</t>
+          <t>Introductory Systems 12 covers how computing changed the world and Ext 5.2D (Should It Exist?) examines a current technology in context. A historical survey is not taught.</t>
         </is>
       </c>
     </row>
@@ -796,7 +797,7 @@
       </c>
       <c r="I8" s="5" t="inlineStr">
         <is>
-          <t>Ext 3.1F (Compiled, Typed, and Running on Something) distinguishes compiled from interpreted software, Discovery Systems 8 separates software from hardware, and Units 5.1 and 5.3 cover how software is actually developed and versioned.</t>
+          <t>Ext 3.1F (Compiled, Typed, and Running on Something) distinguishes compiled from interpreted software, Introductory Systems 8 separates software from hardware, and Units 5.1 and 5.3 cover how software is actually developed and versioned.</t>
         </is>
       </c>
     </row>
@@ -976,7 +977,7 @@
       </c>
       <c r="I12" s="8" t="inlineStr">
         <is>
-          <t>Ext 5.3F (Talking to a Server) traces information flow end to end and Discovery Systems 5 covers a design life cycle. The organizational framing is absent.</t>
+          <t>Ext 5.3F (Talking to a Server) traces information flow end to end and Introductory Systems 5 covers a design life cycle. The organizational framing is absent.</t>
         </is>
       </c>
     </row>
@@ -1054,7 +1055,7 @@
       </c>
       <c r="I14" s="8" t="inlineStr">
         <is>
-          <t>Ext 1.1F (Why a PIN?) covers authentication strength and Ext 5.3G (Secret Messages / HTTPS) covers encryption in transit. Discovery Systems 10 covers phishing.</t>
+          <t>Ext 1.1F (Why a PIN?) covers authentication strength and Ext 5.3G (Secret Messages / HTTPS) covers encryption in transit. Introductory Systems 10 covers phishing.</t>
         </is>
       </c>
     </row>
@@ -1148,7 +1149,7 @@
       </c>
       <c r="I16" s="8" t="inlineStr">
         <is>
-          <t>Discovery Systems 4 teaches flowchart symbols and decision points, and Ext 1.2B (Dependency Map) adds a node-and-arrow structure diagram. Pseudocode notation and UML are not taught.</t>
+          <t>Introductory Systems 4 teaches flowchart symbols and decision points, and Ext 1.2B (Dependency Map) adds a node-and-arrow structure diagram. Pseudocode notation and UML are not taught.</t>
         </is>
       </c>
     </row>
@@ -2047,6 +2048,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="14" t="inlineStr">
         <is>
@@ -2091,7 +2093,7 @@
       </c>
       <c r="B6" s="15" t="inlineStr">
         <is>
-          <t>Discovery Project, Coding strand, project NN (01-17).</t>
+          <t>Introductory Project, Coding strand, project NN (01-17).</t>
         </is>
       </c>
     </row>
@@ -2103,7 +2105,7 @@
       </c>
       <c r="B7" s="15" t="inlineStr">
         <is>
-          <t>Discovery Project, Systems strand, project NN (01-14).</t>
+          <t>Introductory Project, Systems strand, project NN (01-14).</t>
         </is>
       </c>
     </row>
@@ -2203,6 +2205,8 @@
         </is>
       </c>
     </row>
+    <row r="16"/>
+    <row r="17"/>
     <row r="18">
       <c r="A18" s="13" t="inlineStr">
         <is>
@@ -2221,7 +2225,7 @@
 SOURCE NOTE: Standard codes and statements were transcribed from the CodeHS published Indiana Principles of Computing standards framework. Course structure and the graduation requirement were verified against Indiana Department of Education pages. Verify wording against the official IDOE course standards document before using this crosswalk in any formal submission.
 Crosswalk analysis (c) KIPR / Botball Explorer.
 === METHODOLOGY (revised) ===
-Scored against FULL LAB BODIES: reflection prompts, Individual Reflection phases, AI Literacy Bridge sections, and Extension Challenges. Evidence base is 750 reflection prompts and 255 Extension Challenges across 27 C labs, 27 Python labs, and 31 Discovery projects.
+Scored against FULL LAB BODIES: reflection prompts, Individual Reflection phases, AI Literacy Bridge sections, and Extension Challenges. Evidence base is 750 reflection prompts and 255 Extension Challenges across 27 C labs, 27 Python labs, and 31 Introductory projects.
 Scoring rule: Full requires evidence in the core lab flow. Partial is assigned where the only evidence sits in an optional Extension Challenge (labelled 'Finished early?'), or where the standard is only partly met. Cells citing 'Ext N.NL' identify the specific extension so a reviewer can verify placement.</t>
         </is>
       </c>
